--- a/public/ofertas.xlsx
+++ b/public/ofertas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mamustin\Desktop\fire_base_union\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B751E2-8DE1-41EF-98FF-7A87AF856390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA6920A-67C6-4D65-BA1A-0CDD1CF08CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
+    <workbookView xWindow="5925" yWindow="1980" windowWidth="22875" windowHeight="12615" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -524,7 +524,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>6053</v>
+        <v>7500151</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>6</v>

--- a/public/ofertas.xlsx
+++ b/public/ofertas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mamustin\Desktop\fire_base_union\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA6920A-67C6-4D65-BA1A-0CDD1CF08CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB31C1C-7234-4FEE-BD18-8061FF981B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5925" yWindow="1980" windowWidth="22875" windowHeight="12615" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
+    <workbookView xWindow="2835" yWindow="2385" windowWidth="22875" windowHeight="12615" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -524,7 +524,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>7500151</v>
+        <v>7500584</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>6</v>

--- a/public/ofertas.xlsx
+++ b/public/ofertas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mamustin\Desktop\fire_base_union\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\la union\Desktop\fire_base_union\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB31C1C-7234-4FEE-BD18-8061FF981B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4083FDF-0E7C-4D8F-B167-687092C7D650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2835" yWindow="2385" windowWidth="22875" windowHeight="12615" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -191,9 +194,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -231,7 +234,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -337,7 +340,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -479,7 +482,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -488,19 +491,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4190970-C57D-4D00-BE8A-7723D6EF78B5}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1455</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -511,7 +514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3147</v>
       </c>
@@ -519,10 +522,10 @@
         <v>4</v>
       </c>
       <c r="C4" s="3">
-        <v>395000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>410000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>7500584</v>
       </c>
@@ -530,10 +533,10 @@
         <v>6</v>
       </c>
       <c r="C5" s="3">
-        <v>395000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>410000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
@@ -541,10 +544,10 @@
         <v>7</v>
       </c>
       <c r="C6" s="3">
-        <v>395000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>410000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>3148</v>
       </c>
@@ -552,10 +555,10 @@
         <v>5</v>
       </c>
       <c r="C7" s="3">
-        <v>430000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>445000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
@@ -563,10 +566,10 @@
         <v>8</v>
       </c>
       <c r="C8" s="3">
-        <v>430000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>445000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>7500589</v>
       </c>
@@ -574,10 +577,10 @@
         <v>9</v>
       </c>
       <c r="C9" s="3">
-        <v>430000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>445000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>7500148</v>
       </c>
@@ -585,10 +588,10 @@
         <v>10</v>
       </c>
       <c r="C10" s="3">
-        <v>430000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>445000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>14</v>
       </c>
@@ -596,10 +599,10 @@
         <v>11</v>
       </c>
       <c r="C11" s="3">
-        <v>430000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>445000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>6535</v>
       </c>
@@ -607,10 +610,10 @@
         <v>15</v>
       </c>
       <c r="C12" s="3">
-        <v>55000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>57000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>17</v>
       </c>
@@ -618,45 +621,45 @@
         <v>16</v>
       </c>
       <c r="C13" s="3">
-        <v>47000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>49000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>

--- a/public/ofertas.xlsx
+++ b/public/ofertas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\la union\Desktop\fire_base_union\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4083FDF-0E7C-4D8F-B167-687092C7D650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A211A74-6568-4882-99E0-AA14C202E0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
   </bookViews>
@@ -500,7 +500,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>1455</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">

--- a/public/ofertas.xlsx
+++ b/public/ofertas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\la union\Desktop\fire_base_union\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A211A74-6568-4882-99E0-AA14C202E0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97AE7785-D580-47F2-B342-9E979EE55977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
   </bookViews>
@@ -500,7 +500,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>1470</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">

--- a/public/ofertas.xlsx
+++ b/public/ofertas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\la union\Desktop\fire_base_union\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97AE7785-D580-47F2-B342-9E979EE55977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B75DA8D2-FFA7-417B-ADCE-4CBABB149B45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
   </bookViews>
@@ -500,7 +500,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>1485</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">

--- a/public/ofertas.xlsx
+++ b/public/ofertas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\la union\Desktop\fire_base_union\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B75DA8D2-FFA7-417B-ADCE-4CBABB149B45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{507E6255-25B9-4FB6-8027-31FC014BA7A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>codigo</t>
   </si>
@@ -43,45 +43,6 @@
   </si>
   <si>
     <t>eco76</t>
-  </si>
-  <si>
-    <t>eco86</t>
-  </si>
-  <si>
-    <t>275 s201</t>
-  </si>
-  <si>
-    <t>xars92</t>
-  </si>
-  <si>
-    <t>ard1</t>
-  </si>
-  <si>
-    <t>275 rd801</t>
-  </si>
-  <si>
-    <t>295 rd801</t>
-  </si>
-  <si>
-    <t>xard42</t>
-  </si>
-  <si>
-    <t>AR16217038</t>
-  </si>
-  <si>
-    <t>AR9191602HD</t>
-  </si>
-  <si>
-    <t>AR6781703G</t>
-  </si>
-  <si>
-    <t>165/70r13 transmate</t>
-  </si>
-  <si>
-    <t>165/70r13 kingboss</t>
-  </si>
-  <si>
-    <t>KB001</t>
   </si>
 </sst>
 </file>
@@ -522,107 +483,53 @@
         <v>4</v>
       </c>
       <c r="C4" s="3">
-        <v>410000</v>
+        <v>425000</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <v>7500584</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="3">
-        <v>410000</v>
-      </c>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="3">
-        <v>410000</v>
-      </c>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
-        <v>3148</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="3">
-        <v>445000</v>
-      </c>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="3">
-        <v>445000</v>
-      </c>
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
-        <v>7500589</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="3">
-        <v>445000</v>
-      </c>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
-        <v>7500148</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="3">
-        <v>445000</v>
-      </c>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="3">
-        <v>445000</v>
-      </c>
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
-        <v>6535</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="3">
-        <v>57000</v>
-      </c>
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="3">
-        <v>49000</v>
-      </c>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>

--- a/public/ofertas.xlsx
+++ b/public/ofertas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\la union\Desktop\fire_base_union\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{507E6255-25B9-4FB6-8027-31FC014BA7A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EA874F-4C07-4B88-A59D-E7F2DD1F010A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
   </bookViews>
@@ -461,7 +461,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>1495</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">

--- a/public/ofertas.xlsx
+++ b/public/ofertas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\la union\Desktop\fire_base_union\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EA874F-4C07-4B88-A59D-E7F2DD1F010A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B67CEE-7F92-43EB-97FA-A320C5FD21B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
+    <workbookView xWindow="5880" yWindow="0" windowWidth="17160" windowHeight="8928" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -461,7 +461,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>1510</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">

--- a/public/ofertas.xlsx
+++ b/public/ofertas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\la union\Desktop\fire_base_union\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B67CEE-7F92-43EB-97FA-A320C5FD21B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8D8D12-14D7-4158-B419-9B578EFD5C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5880" yWindow="0" windowWidth="17160" windowHeight="8928" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
+    <workbookView xWindow="5880" yWindow="1044" windowWidth="17160" windowHeight="8928" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -461,7 +461,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>1495</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">

--- a/public/ofertas.xlsx
+++ b/public/ofertas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\la union\Desktop\fire_base_union\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8D8D12-14D7-4158-B419-9B578EFD5C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4535AEAB-36D2-4165-A7B1-87231264C0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5880" yWindow="1044" windowWidth="17160" windowHeight="8928" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -461,7 +461,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>1505</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">

--- a/public/ofertas.xlsx
+++ b/public/ofertas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\la union\Desktop\fire_base_union\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4535AEAB-36D2-4165-A7B1-87231264C0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{721495FE-22BE-4CDE-92DA-7C2409E3FF6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>codigo</t>
   </si>
@@ -40,9 +40,6 @@
   </si>
   <si>
     <t>dolar</t>
-  </si>
-  <si>
-    <t>eco76</t>
   </si>
 </sst>
 </file>
@@ -476,15 +473,9 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <v>3147</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="3">
-        <v>425000</v>
-      </c>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>

--- a/public/ofertas.xlsx
+++ b/public/ofertas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\la union\Desktop\fire_base_union\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{721495FE-22BE-4CDE-92DA-7C2409E3FF6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89487A29-C39F-4274-8DFF-1A63AE419686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>codigo</t>
   </si>
@@ -40,6 +40,18 @@
   </si>
   <si>
     <t>dolar</t>
+  </si>
+  <si>
+    <t>AR16217038</t>
+  </si>
+  <si>
+    <t>AR6781703G</t>
+  </si>
+  <si>
+    <t>AR7971602HD</t>
+  </si>
+  <si>
+    <t>AR9191602HD</t>
   </si>
 </sst>
 </file>
@@ -473,69 +485,121 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
+      <c r="A4" s="3">
+        <v>3147</v>
+      </c>
       <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
+      <c r="C4" s="3">
+        <v>415000</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="3"/>
+      <c r="A5" s="3">
+        <v>104058</v>
+      </c>
       <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
+      <c r="C5" s="3">
+        <v>587000</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
+      <c r="A6" s="3">
+        <v>3148</v>
+      </c>
       <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
+      <c r="C6" s="3">
+        <v>455000</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
+      <c r="A7" s="3">
+        <v>4214</v>
+      </c>
       <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
+      <c r="C7" s="3">
+        <v>446000</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
+      <c r="A8" s="3">
+        <v>103269</v>
+      </c>
       <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
+      <c r="C8" s="3">
+        <v>445000</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
+      <c r="A9">
+        <v>7500584</v>
+      </c>
       <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
+      <c r="C9" s="3">
+        <v>415000</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="3"/>
+      <c r="A10">
+        <v>7500589</v>
+      </c>
       <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
+      <c r="C10" s="3">
+        <v>455000</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
+      <c r="A11">
+        <v>7500148</v>
+      </c>
       <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
+      <c r="C11" s="3">
+        <v>455000</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
+      <c r="A12">
+        <v>7500150</v>
+      </c>
       <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
+      <c r="C12" s="3">
+        <v>500000</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
       <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
+      <c r="C13" s="3">
+        <v>415000</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
+      <c r="A14" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
+      <c r="C14" s="3">
+        <v>455000</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
       <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
+      <c r="C15" s="3">
+        <v>415000</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
       <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
+      <c r="C16" s="3">
+        <v>455000</v>
+      </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>

--- a/public/ofertas.xlsx
+++ b/public/ofertas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\la union\Desktop\fire_base_union\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89487A29-C39F-4274-8DFF-1A63AE419686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C72D9E90-D5B4-4B9C-9E2A-7D696642A2F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -470,7 +470,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>1515</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
